--- a/evaluation/det_gemini_realset.xlsx
+++ b/evaluation/det_gemini_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.5125</v>
+        <v>0.75625</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.6154220815200304</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.4458333333333333</v>
+        <v>0.7053728070175438</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.058823529411764705</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.03687169312169313</v>
+        <v>0.40015627666837345</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.4965874247117617</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5872574955908288</v>
+        <v>0.7845378387045053</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.8761904761904762</v>
       </c>
     </row>
     <row r="6">
@@ -461,7 +461,7 @@
         <v>0.14005587822514343</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.038461538461538464</v>
+        <v>0.31089743589743585</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.13256448412698413</v>
+        <v>0.5085899343711844</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7738505747126436</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         <v>0.75</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.6493055555555556</v>
+        <v>0.8246527777777778</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.13124999999999998</v>
+        <v>0.5248086734693878</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.40033959725437446</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.2523809523809524</v>
+        <v>0.5949404761904762</v>
       </c>
     </row>
     <row r="16">
@@ -609,7 +609,7 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.8100649350649352</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.8444144592599948</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.5816666666666668</v>
+        <v>0.7618478260869566</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.9820136456817886</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9555555555555557</v>
+        <v>0.9777777777777779</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.5799820693848332</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.11607142857142858</v>
+        <v>0.48530844155844155</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.6</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.5</v>
+        <v>0.6447368421052632</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.48369640170019296</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.3055555555555555</v>
+        <v>0.613562091503268</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/det_gemini_realset.xlsx
+++ b/evaluation/det_gemini_realset.xlsx
@@ -333,7 +333,7 @@
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
     <col width="5.5" min="2" max="2" bestFit="1" customWidth="1"/>
     <col width="25.3" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="4" max="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,7 +349,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.75625</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="2">
@@ -365,7 +365,7 @@
         <v>0.6154220815200304</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.7053728070175438</v>
+        <v>0.4301900584795321</v>
       </c>
     </row>
     <row r="3">
@@ -381,7 +381,7 @@
         <v>0.058823529411764705</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.40015627666837345</v>
+        <v>0.028149357114410883</v>
       </c>
     </row>
     <row r="4">
@@ -397,7 +397,7 @@
         <v>0.4965874247117617</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.7845378387045053</v>
+        <v>0.5765800865800865</v>
       </c>
     </row>
     <row r="5">
@@ -413,7 +413,7 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8761904761904762</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="6">
@@ -461,7 +461,7 @@
         <v>0.14005587822514343</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.31089743589743585</v>
+        <v>0.022435897435897436</v>
       </c>
     </row>
     <row r="9">
@@ -477,7 +477,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.5085899343711844</v>
+        <v>0.11726858211233211</v>
       </c>
     </row>
     <row r="10">
@@ -493,7 +493,7 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.7738505747126436</v>
+        <v>0.5741379310344827</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         <v>0.75</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>0.8246527777777778</v>
+        <v>0.6493055555555556</v>
       </c>
     </row>
     <row r="14">
@@ -557,7 +557,7 @@
         <v>0.07692307692307693</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>0.5248086734693878</v>
+        <v>0.12053571428571427</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         <v>0.40033959725437446</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>0.5949404761904762</v>
+        <v>0.23660714285714285</v>
       </c>
     </row>
     <row r="16">
@@ -609,7 +609,7 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0.8100649350649352</v>
+        <v>0.6282467532467533</v>
       </c>
     </row>
     <row r="18">
@@ -625,7 +625,7 @@
         <v>0.8444144592599948</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0.7618478260869566</v>
+        <v>0.5479468599033818</v>
       </c>
     </row>
     <row r="19">
@@ -641,7 +641,7 @@
         <v>0.9820136456817886</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>0.9777777777777779</v>
+        <v>0.9555555555555557</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         <v>0.5799820693848332</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>0.48530844155844155</v>
+        <v>0.09918831168831169</v>
       </c>
     </row>
     <row r="21">
@@ -673,7 +673,7 @@
         <v>0.6</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>0.6447368421052632</v>
+        <v>0.39473684210526316</v>
       </c>
     </row>
     <row r="22">
@@ -689,7 +689,7 @@
         <v>0.48369640170019296</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>0.613562091503268</v>
+        <v>0.2815904139433551</v>
       </c>
     </row>
   </sheetData>
